--- a/histograms/histogram_Wave_length_min__nm.xlsx
+++ b/histograms/histogram_Wave_length_min__nm.xlsx
@@ -445,7 +445,7 @@
         <v>209.5</v>
       </c>
       <c r="B2" t="n">
-        <v>5131</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>228.5</v>
       </c>
       <c r="B3" t="n">
-        <v>13138</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>247.5</v>
       </c>
       <c r="B4" t="n">
-        <v>121</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         <v>285.5</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>304.5</v>
       </c>
       <c r="B7" t="n">
-        <v>2739</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -509,7 +509,7 @@
         <v>361.5</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         <v>399.5</v>
       </c>
       <c r="B12" t="n">
-        <v>2003</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>418.5</v>
       </c>
       <c r="B13" t="n">
-        <v>2130</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
